--- a/toydata/projects.xlsx
+++ b/toydata/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roywilliams/Documents/grantPlanning/PAM.nb/toydata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rwillia5/Documents/PAM.nb/toydata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE15CF-1131-3C48-9575-269A4E7907C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD1DAC6-9CE8-6947-988C-E4BF70C5FB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="1920" windowWidth="26020" windowHeight="15860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6140" yWindow="2860" windowWidth="30080" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -748,7 +748,7 @@
     <col min="8" max="8" width="34.1640625" customWidth="1"/>
     <col min="9" max="9" width="13.1640625" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4" customWidth="1"/>
+    <col min="11" max="11" width="3.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="5" customWidth="1"/>
     <col min="14" max="14" width="11.83203125" style="5" customWidth="1"/>
@@ -864,7 +864,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="1">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="J2" s="1">
         <v>20000</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="L2" s="1">
         <f t="shared" ref="L2:L9" si="0">I2-J2</f>
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="M2" s="6">
         <v>44651</v>
@@ -936,17 +936,17 @@
         <v>29</v>
       </c>
       <c r="I3" s="1">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="J3" s="1">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
       <c r="L3" s="1">
         <f t="shared" si="0"/>
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="M3" s="6">
         <v>44651</v>
@@ -999,15 +999,15 @@
         <v>92</v>
       </c>
       <c r="I4" s="1">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J4" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="M4" s="6">
         <v>44651</v>
@@ -1041,15 +1041,15 @@
         <v>93</v>
       </c>
       <c r="I5" s="1">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J5" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="M5" s="6">
         <v>44651</v>
@@ -1083,15 +1083,15 @@
         <v>27</v>
       </c>
       <c r="I6" s="1">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="J6" s="1">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1">
         <f t="shared" si="0"/>
-        <v>170000</v>
+        <v>40000</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>99</v>
@@ -1125,15 +1125,15 @@
         <v>29</v>
       </c>
       <c r="I7" s="1">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>99</v>
@@ -1167,15 +1167,15 @@
         <v>92</v>
       </c>
       <c r="I8" s="1">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J8" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>99</v>
@@ -1209,15 +1209,15 @@
         <v>93</v>
       </c>
       <c r="I9" s="1">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J9" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>99</v>

--- a/toydata/projects.xlsx
+++ b/toydata/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rwillia5/Documents/PAM.nb/toydata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD1DAC6-9CE8-6947-988C-E4BF70C5FB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C69BB1-F574-BE44-B865-7D9F7C87FA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="2860" windowWidth="30080" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3400" yWindow="760" windowWidth="28540" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -999,7 +999,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J4" s="1">
         <v>2000</v>
@@ -1007,7 +1007,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="M4" s="6">
         <v>44651</v>
@@ -1041,7 +1041,7 @@
         <v>93</v>
       </c>
       <c r="I5" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J5" s="1">
         <v>2000</v>
@@ -1049,7 +1049,7 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="M5" s="6">
         <v>44651</v>
